--- a/tests/build_food_db/fixtures/ciqual_slice.xlsx
+++ b/tests/build_food_db/fixtures/ciqual_slice.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table Ciqual 2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="composition nutritionnelle" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -929,7 +929,6 @@
           <t>1519</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>7,15</t>
